--- a/testdata/regions_three.xlsx
+++ b/testdata/regions_three.xlsx
@@ -582,7 +582,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>290.00</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>300.00</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>110.00</t>
+          <t>310.00</t>
         </is>
       </c>
     </row>
